--- a/SE stuff/Maria Model/thickness_content_only.xlsx
+++ b/SE stuff/Maria Model/thickness_content_only.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liame\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liame\OneDrive\Documents\Summer26\SE stuff\Maria Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6585A3A-426A-4A12-8C3D-DD9A97FE16E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B775E62-5272-4210-8A05-8398B3588414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>Sample ID</t>
   </si>
@@ -161,6 +161,24 @@
   </si>
   <si>
     <t>X-Bi content RBS UNC (%)</t>
+  </si>
+  <si>
+    <t>190919A</t>
+  </si>
+  <si>
+    <t>190920A</t>
+  </si>
+  <si>
+    <t>190923A</t>
+  </si>
+  <si>
+    <t>191021A</t>
+  </si>
+  <si>
+    <t>191022A</t>
+  </si>
+  <si>
+    <t>191022B</t>
   </si>
 </sst>
 </file>
@@ -204,13 +222,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -378,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1016,6 +1037,72 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="2">
+        <v>9</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="2">
+        <v>19</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="2">
+        <v>36</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="2">
+        <v>83</v>
+      </c>
+      <c r="C33" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="2">
+        <v>31</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="2">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SE stuff/Maria Model/thickness_content_only.xlsx
+++ b/SE stuff/Maria Model/thickness_content_only.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liame\OneDrive\Documents\Summer26\SE stuff\Maria Model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb7a53591c131afc/Documents/Summer26/SE stuff/Maria Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B775E62-5272-4210-8A05-8398B3588414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -16,6 +16,7 @@
     <sheet name="Thickness_Content" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
